--- a/Lung Cancer Prediction with Explainable Region Prioritization.xlsx
+++ b/Lung Cancer Prediction with Explainable Region Prioritization.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Fyp Lung Cancer\FYP-Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pern-my.sharepoint.com/personal/03-134231-005_student_bahria_edu_pk/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24B20E13-8FD4-41DC-997C-D6471C370B18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7FC0444-FBA4-41F5-A06C-30D5744035AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
